--- a/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-explanation-requested.xlsx
+++ b/r5-aist-trustworthyai-main/StructureDefinition-eu-ai-explanation-requested.xlsx
@@ -9,14 +9,11 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$6</definedName>
-  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="105">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T08:40:47+00:00</t>
+    <t>2026-06-18T12:04:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -323,9 +320,6 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -472,21 +466,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -814,7 +793,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
@@ -917,7 +896,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>78</v>
       </c>
@@ -1020,7 +999,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>86</v>
       </c>
@@ -1123,7 +1102,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>93</v>
       </c>
@@ -1247,22 +1226,22 @@
         <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="I6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="J6" t="s" s="2">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s" s="2">
         <v>100</v>
       </c>
-      <c r="I6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s" s="2">
-        <v>18</v>
-      </c>
-      <c r="K6" t="s" s="2">
+      <c r="L6" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1322,34 +1301,16 @@
         <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ6" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="AJ6" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>98</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK6">
-    <filterColumn colId="7">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="27">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI5">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>